--- a/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -690,7 +690,7 @@
     <t>To support grouped procedures (one imaging study supporting multiple ordered procedures, e.g. chest/abdomen/pelvis CT).</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">type:$this}
 </t>
   </si>
   <si>
@@ -719,6 +719,139 @@
     <t>Référence à la demande d'examen contenant l'Accession Number</t>
   </si>
   <si>
+    <t>ImagingStudy.basedOn:serviceRequestAccessionNumber.id</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn:serviceRequestAccessionNumber.extension</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn:serviceRequestAccessionNumber.reference</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn:serviceRequestAccessionNumber.type</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn:serviceRequestAccessionNumber.identifier</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn:serviceRequestAccessionNumber.display</t>
+  </si>
+  <si>
+    <t>ImagingStudy.basedOn.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>ImagingStudy.referrer</t>
   </si>
   <si>
@@ -867,9 +1000,6 @@
     <t>The code for the performed procedure type.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>The performed procedure type.</t>
   </si>
   <si>
@@ -982,10 +1112,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Institution-generated description</t>
   </si>
   <si>
@@ -1017,25 +1143,7 @@
     <t>ImagingStudy.series.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>ImagingStudy.series.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>ImagingStudy.series.modifierExtension</t>
@@ -1336,10 +1444,6 @@
   </si>
   <si>
     <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
   </si>
   <si>
     <t>ImagingStudy.series.instance.extension:number-of-frames</t>
@@ -1763,10 +1867,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO60"/>
+  <dimension ref="A1:AO66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.11328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.21875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.13671875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.09765625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1790,11 +1894,11 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="34.12109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="76.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="32.90234375" customWidth="true" bestFit="true" hidden="true"/>
@@ -4040,11 +4144,11 @@
         <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4060,7 +4164,7 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>226</v>
@@ -4120,7 +4224,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4132,19 +4236,19 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4155,11 +4259,11 @@
         <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4175,18 +4279,20 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N21" s="2"/>
+      <c r="N21" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4223,19 +4329,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4247,19 +4353,19 @@
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>78</v>
@@ -4267,7 +4373,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>238</v>
@@ -4281,7 +4387,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
@@ -4293,20 +4399,18 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>243</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4354,16 +4458,16 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -4372,28 +4476,28 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>246</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4403,7 +4507,7 @@
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
@@ -4412,15 +4516,17 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4445,13 +4551,13 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
@@ -4469,7 +4575,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4487,10 +4593,10 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>251</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4501,18 +4607,18 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
@@ -4527,15 +4633,17 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>247</v>
+        <v>161</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4584,7 +4692,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4602,10 +4710,10 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4616,10 +4724,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4642,15 +4750,17 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -4699,7 +4809,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4714,13 +4824,13 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>263</v>
+        <v>132</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4731,21 +4841,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4757,13 +4867,13 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4790,13 +4900,13 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -4814,13 +4924,13 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
@@ -4829,16 +4939,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>78</v>
@@ -4846,21 +4956,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>274</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -4872,18 +4982,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4931,13 +5039,13 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
@@ -4946,27 +5054,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AO27" t="s" s="2">
-        <v>283</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4989,16 +5097,20 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5022,11 +5134,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -5044,7 +5158,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5059,41 +5173,41 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>291</v>
+        <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
@@ -5102,13 +5216,13 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5159,13 +5273,13 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
@@ -5174,38 +5288,38 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>293</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>291</v>
+        <v>78</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>298</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -5217,13 +5331,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5274,13 +5388,13 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
@@ -5289,13 +5403,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5306,14 +5420,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>306</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5332,13 +5446,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5389,7 +5503,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5404,13 +5518,13 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -5419,26 +5533,26 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
@@ -5447,13 +5561,13 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5480,13 +5594,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>78</v>
+        <v>313</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -5504,7 +5618,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5519,13 +5633,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>306</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -5536,10 +5650,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5559,19 +5673,21 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
@@ -5619,46 +5735,46 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK33" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>321</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>78</v>
+        <v>322</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5674,20 +5790,18 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5712,13 +5826,11 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5736,7 +5848,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5748,19 +5860,19 @@
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -5768,14 +5880,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5788,26 +5900,22 @@
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>334</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5855,7 +5963,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5867,41 +5975,41 @@
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5913,20 +6021,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>91</v>
+        <v>341</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5938,7 +6042,7 @@
         <v>78</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>336</v>
+        <v>78</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>78</v>
@@ -5974,13 +6078,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -5989,13 +6093,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6006,14 +6110,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6032,13 +6136,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6053,7 +6157,7 @@
         <v>78</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>78</v>
@@ -6089,7 +6193,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6107,10 +6211,10 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6121,14 +6225,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6147,13 +6251,13 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>176</v>
+        <v>353</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6180,11 +6284,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6202,13 +6308,13 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
@@ -6220,10 +6326,10 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>180</v>
+        <v>356</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6234,14 +6340,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>352</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6257,16 +6363,16 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>227</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>228</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6281,7 +6387,7 @@
         <v>78</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>78</v>
@@ -6317,7 +6423,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>229</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6329,16 +6435,16 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>356</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6349,21 +6455,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>358</v>
+        <v>134</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6372,18 +6478,20 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>247</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -6432,28 +6540,28 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>361</v>
+        <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6464,14 +6572,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>78</v>
+        <v>360</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6484,25 +6592,25 @@
         <v>78</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>363</v>
+        <v>135</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>366</v>
+        <v>138</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>367</v>
+        <v>144</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -6551,7 +6659,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6563,13 +6671,13 @@
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>244</v>
+        <v>132</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6583,18 +6691,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -6609,16 +6717,20 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6630,7 +6742,7 @@
         <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>78</v>
@@ -6642,11 +6754,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>372</v>
+        <v>78</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6664,10 +6778,10 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -6682,38 +6796,38 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -6722,13 +6836,13 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>176</v>
+        <v>289</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6743,7 +6857,7 @@
         <v>78</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>78</v>
@@ -6755,11 +6869,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6777,7 +6893,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6795,7 +6911,7 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>379</v>
@@ -6807,7 +6923,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>380</v>
       </c>
@@ -6816,17 +6932,17 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6835,7 +6951,7 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>381</v>
+        <v>176</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>382</v>
@@ -6868,13 +6984,11 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6895,10 +7009,10 @@
         <v>380</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
@@ -6910,10 +7024,10 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -6924,14 +7038,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6950,7 +7064,7 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>387</v>
@@ -6971,7 +7085,7 @@
         <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>78</v>
@@ -7007,7 +7121,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7025,10 +7139,10 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>207</v>
+        <v>350</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7039,21 +7153,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>78</v>
@@ -7065,20 +7179,16 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N46" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>395</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7126,13 +7236,13 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>78</v>
@@ -7141,13 +7251,13 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>235</v>
+        <v>298</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7158,10 +7268,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7172,7 +7282,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7181,19 +7291,23 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>307</v>
+        <v>397</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>318</v>
+        <v>398</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7241,25 +7355,25 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>320</v>
+        <v>396</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7273,21 +7387,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>134</v>
+        <v>403</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7296,20 +7410,18 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7334,13 +7446,11 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>78</v>
+        <v>406</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7358,28 +7468,28 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>324</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>321</v>
+        <v>407</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -7388,48 +7498,44 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>327</v>
+        <v>410</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7453,13 +7559,11 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7477,28 +7581,28 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>329</v>
+        <v>409</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>132</v>
+        <v>407</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7509,10 +7613,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7523,7 +7627,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7535,18 +7639,16 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>267</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7570,13 +7672,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7594,13 +7696,13 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
@@ -7612,10 +7714,10 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>235</v>
+        <v>418</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7626,10 +7728,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7637,7 +7739,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -7652,13 +7754,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>408</v>
+        <v>202</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7709,10 +7811,10 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>89</v>
@@ -7727,56 +7829,60 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>410</v>
+        <v>207</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>412</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7824,7 +7930,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7839,13 +7945,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>78</v>
+        <v>430</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>416</v>
+        <v>277</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7856,10 +7962,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7882,13 +7988,13 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>318</v>
+        <v>227</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7939,7 +8045,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>320</v>
+        <v>229</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7957,7 +8063,7 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -7971,14 +8077,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8000,12 +8106,14 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>419</v>
+        <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8042,17 +8150,19 @@
         <v>78</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AC54" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>324</v>
+        <v>236</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8070,7 +8180,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8084,44 +8194,46 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>78</v>
+        <v>360</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>424</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>425</v>
+        <v>361</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8169,7 +8281,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8178,7 +8290,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>427</v>
+        <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>140</v>
@@ -8187,7 +8299,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8201,45 +8313,43 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>327</v>
+        <v>436</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>144</v>
+        <v>438</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8264,13 +8374,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8288,25 +8398,25 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>329</v>
+        <v>435</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>132</v>
+        <v>277</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8320,14 +8430,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8343,23 +8453,19 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>91</v>
+        <v>442</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8371,7 +8477,7 @@
         <v>78</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>78</v>
@@ -8407,7 +8513,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8425,38 +8531,38 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>337</v>
+        <v>444</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>78</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
@@ -8465,13 +8571,13 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>176</v>
+        <v>353</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8498,11 +8604,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8520,13 +8628,13 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
@@ -8538,10 +8646,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -8552,14 +8660,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8578,13 +8686,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>446</v>
+        <v>227</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>447</v>
+        <v>228</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8599,7 +8707,7 @@
         <v>78</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>78</v>
@@ -8635,7 +8743,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>444</v>
+        <v>229</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8647,16 +8755,16 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>448</v>
+        <v>230</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8667,10 +8775,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8681,7 +8789,7 @@
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8693,17 +8801,15 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>307</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8740,50 +8846,748 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>450</v>
+        <v>236</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO60" t="s" s="2">
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Y64" s="2"/>
+      <c r="Z64" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO60">
+  <autoFilter ref="A1:AO66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8793,7 +9597,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1049,7 +1049,7 @@
     <t>Description of clinical condition indicating why the ImagingStudy was requested.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imagerie-objectif-reference-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-imagerie-objectif-reference-cisis|20260916095454</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1314,7 +1314,7 @@
     <t>The laterality of the (possibly paired) anatomic structures examined. E.g., the left knee, both lungs, or unpaired abdomen. If present, shall be consistent with any laterality information indicated in ImagingStudy.series.bodySite.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modificateur-topographique-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modificateur-topographique-cisis|20260916095453</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1507,7 +1507,7 @@
     <t>DICOM instance  type.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis|20260916095453</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>

--- a/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
